--- a/results/job_matches_2026-09-22.xlsx
+++ b/results/job_matches_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer - Gen AI</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311b3d4d764c329</t>
+          <t>https://www.indeed.com/viewjob?jk=947423e1243398ca</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pj Dick-Trumbull-Lindy Group</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=9311b3d4d764c329</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pj Dick-Trumbull-Lindy Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wexford, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e707c3d7c8fd8897</t>
+          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Larry H. Miller</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Wexford, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740a0acafa426fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e707c3d7c8fd8897</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Data and Integration</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, Azure, Databricks, GCP, BigQuery, Scala, Kafka</t>
+          <t>AWS, Step Functions, S3, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cef3158b77fad33</t>
+          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Larry H. Miller</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SNS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=6740a0acafa426fb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Engineering</t>
+          <t>Sr Software Engineer - Data and Integration</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FourLeaf Federal Credit Union</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, SQS, SNS, Azure, Databricks, GCP, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18438b84428c657e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cef3158b77fad33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Orgill, Inc.</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Collierville, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full stack Developer</t>
+          <t>Solutions Architect - Data Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phizenix</t>
+          <t>FourLeaf Federal Credit Union</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb607626dcebb23</t>
+          <t>https://www.indeed.com/viewjob?jk=18438b84428c657e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior Backend Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ecdb24fded8712c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad676d0583954a5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mid-Level Java Full Stack Developer</t>
+          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Orgill, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Collierville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Full stack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ShipStation Global</t>
+          <t>Phizenix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=028e43335938f143</t>
+          <t>https://www.indeed.com/viewjob?jk=deb607626dcebb23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Mid-Level Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ShipStation Global</t>
+          <t>Antra, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5966248554dc0bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6329)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>ShipStation Global</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4007bc63b344853</t>
+          <t>https://www.indeed.com/viewjob?jk=028e43335938f143</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>ShipStation Global</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bea3079274e464</t>
+          <t>https://www.indeed.com/viewjob?jk=5966248554dc0bb5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Data Engineer IV (6329)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77aeab60d6ba5f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e4007bc63b344853</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer, Expert</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f790e3f3013d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6425afe8b03c9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781fa7970847c14</t>
+          <t>https://www.indeed.com/viewjob?jk=69bea3079274e464</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boats Group</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, ECS, IAM, RDS, Snowflake, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917ce891fbb59294</t>
+          <t>https://www.indeed.com/viewjob?jk=77aeab60d6ba5f5a</t>
         </is>
       </c>
     </row>
@@ -1138,20 +1138,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d93b899dbf5eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=e448fd868464b75d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Data Engineer, Expert</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f9f03cfec0fc88</t>
+          <t>https://www.indeed.com/viewjob?jk=f790e3f3013d99d9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d4fb8c5ae21e05</t>
+          <t>https://www.indeed.com/viewjob?jk=b781fa7970847c14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Summer 2027 Intern: Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef57e790e48920b</t>
+          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Veradigm</t>
+          <t>Boats Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Athena, S3, SQS, ECS, IAM, RDS, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febe1e7e8d9c2705</t>
+          <t>https://www.indeed.com/viewjob?jk=917ce891fbb59294</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deepwatch</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Splunk</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
+          <t>https://www.indeed.com/viewjob?jk=1d93b899dbf5eaf4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer II</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69597557ab5f1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=54f9f03cfec0fc88</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Veradigm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb60941e0eaba4f</t>
+          <t>https://www.indeed.com/viewjob?jk=febe1e7e8d9c2705</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Deepwatch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a89b0de664aa93</t>
+          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c02567e875c724</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef57e790e48920b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Lafayette, IN, US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a9d0a4fe41bcb8</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer, Information Systems Specialist 7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9908194ee52c240</t>
+          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d06caa1f573b5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a69597557ab5f1ab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80229a4fad29b8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb60941e0eaba4f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e702bf50ec0d208</t>
+          <t>https://www.indeed.com/viewjob?jk=31a89b0de664aa93</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8537a87f0d58bfca</t>
+          <t>https://www.indeed.com/viewjob?jk=83c02567e875c724</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Specialist, Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BetaNXT</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Lafayette, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
+          <t>https://www.indeed.com/viewjob?jk=52a9d0a4fe41bcb8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full- stack Engineer 4 - Capital One Shopping Tech (Categories Team) (Remote - Eligible)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7893e5b1e4d9ff22</t>
+          <t>https://www.indeed.com/viewjob?jk=e9908194ee52c240</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data and Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
+          <t>https://www.indeed.com/viewjob?jk=4d06caa1f573b5e4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac96998021af3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=80229a4fad29b8e0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c19b3b22378c8efc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e702bf50ec0d208</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Direct Client for Contact Center Architect Healthcare with AWS Connect</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Southwest, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3285dc43ed16da74</t>
+          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAP S/4HANA Material Master Solution Architect / Senior MM Architect</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sdna global</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63f66f6aa5ca957</t>
+          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>ProBridge - Junior Snowflake Database Administrator</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02c5537c36a52ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b276cb63efa2d3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Contact center Architect - Amazon Connect</t>
+          <t>ProBridge - Junior Snowflake Database Administrator</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RPA INFOTECH INDIA</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8011e2e01cd1c12</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab9ab4b8aed789a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aegis Mobile</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Chestertown, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Power BI, Tableau, MLOps, Git, Python</t>
+          <t>AWS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cddb3162ff0a10d8</t>
+          <t>https://www.indeed.com/viewjob?jk=54102d5fe6d163bd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Multi- Cloud Solutions Architect</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cywarden, Inc.</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, IAM, Azure, GCP, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90096161c263b413</t>
+          <t>https://www.indeed.com/viewjob?jk=8537a87f0d58bfca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Database Administrator - San Juan, PR</t>
+          <t>Senior Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BetaNXT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full- stack Engineer 4 - Capital One Shopping Tech (Categories Team) (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7519f106646cfafb</t>
+          <t>https://www.indeed.com/viewjob?jk=7893e5b1e4d9ff22</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Technical Implementations Specialist (US)</t>
+          <t>Senior Disputes Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MEASURED</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d911c664f1ca9e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Golang, AWS)</t>
+          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Aledade</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9769cef0a6e3ea3c</t>
+          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dc299c4f5e424b</t>
+          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,15 +2298,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, Power BI, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cef3fbaab3f7c3</t>
+          <t>https://www.indeed.com/viewjob?jk=aac96998021af3ad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Superior Automotive Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, BigQuery, Dataflow, Vertex AI, Dimensional Modeling, dbt, Power BI, Tableau, Splunk, CI/CD</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b32326f024eeaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=c19b3b22378c8efc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Direct Client for Contact Center Architect Healthcare with AWS Connect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd065039757b55c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3285dc43ed16da74</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Developer in Test</t>
+          <t>SAP S/4HANA Material Master Solution Architect / Senior MM Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>sdna global</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56dd2ecf0c554e</t>
+          <t>https://www.indeed.com/viewjob?jk=d63f66f6aa5ca957</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=078b97b2887a3962</t>
+          <t>https://www.indeed.com/viewjob?jk=b02c5537c36a52ab</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Java Developer (SAP BTP/CAP)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261609512021b9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Java Developer (SAP BTP/CAP)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d251cc0fd62f24</t>
+          <t>https://www.indeed.com/viewjob?jk=7519f106646cfafb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Database Administrator I</t>
+          <t>Database Administrator - San Juan, PR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Transcor Data Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,40 +2561,600 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83390bad559122e2</t>
+          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Sr. Technical Implementations Specialist (US)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Aegis Mobile</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Power BI, Tableau, MLOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cddb3162ff0a10d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Activated Insights</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d911c664f1ca9e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ness Digital Engineering</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RCH Solutions</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Container Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0022787a9f1c8382</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ness Digital Engineering</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19dc299c4f5e424b</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, Power BI, Terraform</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8cef3fbaab3f7c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Superior Automotive Group</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>IAM, BigQuery, Dataflow, Vertex AI, Dimensional Modeling, dbt, Power BI, Tableau, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b32326f024eeaf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>All IT Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80b9a73315ee85ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd065039757b55c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Developer in Test</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d56dd2ecf0c554e</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Trimark Associates, Inc.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Folsom, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (SAP BTP/CAP)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=261609512021b9dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (SAP BTP/CAP)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88d251cc0fd62f24</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=078b97b2887a3962</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>Software Engineer III- Java/Python, SQL, Databricks</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>JPMorganChase</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D78" t="n">
         <v>10.4</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, Tableau</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d42fb889c5ed759</t>
         </is>

--- a/results/job_matches_2026-09-22.xlsx
+++ b/results/job_matches_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Data Engineer 4 (Python, AWS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pj Dick-Trumbull-Lindy Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6785ed8543590d56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wexford, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e707c3d7c8fd8897</t>
+          <t>https://www.indeed.com/viewjob?jk=30216af3fb095a16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Pj Dick-Trumbull-Lindy Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, S3, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
+          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Larry H. Miller</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Wexford, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740a0acafa426fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e707c3d7c8fd8897</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Data and Integration</t>
+          <t>Data Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, Azure, Databricks, GCP, BigQuery, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cef3158b77fad33</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc3d67e2533b3c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Step Functions, S3, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Engineering</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FourLeaf Federal Credit Union</t>
+          <t>Larry H. Miller</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SNS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18438b84428c657e</t>
+          <t>https://www.indeed.com/viewjob?jk=6740a0acafa426fb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer - Data and Integration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, SQS, SNS, Azure, Databricks, GCP, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad676d0583954a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9cef3158b77fad33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Orgill, Inc.</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Collierville, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full stack Developer</t>
+          <t>Solutions Architect - Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Phizenix</t>
+          <t>FourLeaf Federal Credit Union</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb607626dcebb23</t>
+          <t>https://www.indeed.com/viewjob?jk=18438b84428c657e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mid-Level Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad676d0583954a5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ShipStation Global</t>
+          <t>Orgill, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Collierville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=028e43335938f143</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Full stack Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ShipStation Global</t>
+          <t>Phizenix</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5966248554dc0bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=deb607626dcebb23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6329)</t>
+          <t>Mid-Level Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Antra, Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4007bc63b344853</t>
+          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Data Engineer IV (6329)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6425afe8b03c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e4007bc63b344853</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>ShipStation Global</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bea3079274e464</t>
+          <t>https://www.indeed.com/viewjob?jk=028e43335938f143</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>ShipStation Global</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77aeab60d6ba5f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=5966248554dc0bb5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Direct Travel</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e448fd868464b75d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6425afe8b03c9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, Expert</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f790e3f3013d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=69bea3079274e464</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781fa7970847c14</t>
+          <t>https://www.indeed.com/viewjob?jk=77aeab60d6ba5f5a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern: Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Live Oak Bank</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
+          <t>https://www.indeed.com/viewjob?jk=e448fd868464b75d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer, Expert</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Boats Group</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, ECS, IAM, RDS, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917ce891fbb59294</t>
+          <t>https://www.indeed.com/viewjob?jk=f790e3f3013d99d9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d93b899dbf5eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=b781fa7970847c14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Summer 2027 Intern: Data Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f9f03cfec0fc88</t>
+          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Veradigm</t>
+          <t>Boats Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Athena, S3, SQS, ECS, IAM, RDS, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febe1e7e8d9c2705</t>
+          <t>https://www.indeed.com/viewjob?jk=917ce891fbb59294</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deepwatch</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Splunk</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
+          <t>https://www.indeed.com/viewjob?jk=1d93b899dbf5eaf4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef57e790e48920b</t>
+          <t>https://www.indeed.com/viewjob?jk=54f9f03cfec0fc88</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Database Engineer, Information Systems Specialist 7</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Veradigm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
+          <t>https://www.indeed.com/viewjob?jk=febe1e7e8d9c2705</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Deepwatch</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69597557ab5f1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb60941e0eaba4f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef57e790e48920b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a89b0de664aa93</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer, Information Systems Specialist 7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c02567e875c724</t>
+          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>West Lafayette, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a9d0a4fe41bcb8</t>
+          <t>https://www.indeed.com/viewjob?jk=a69597557ab5f1ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9908194ee52c240</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb60941e0eaba4f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d06caa1f573b5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=31a89b0de664aa93</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80229a4fad29b8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=83c02567e875c724</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>West Lafayette, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e702bf50ec0d208</t>
+          <t>https://www.indeed.com/viewjob?jk=52a9d0a4fe41bcb8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Southwest, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e9908194ee52c240</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d06caa1f573b5e4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ProBridge - Junior Snowflake Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b276cb63efa2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=80229a4fad29b8e0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ProBridge - Junior Snowflake Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Xenon7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab9ab4b8aed789a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e702bf50ec0d208</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chestertown, MD, US USA</t>
+          <t>Southwest, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54102d5fe6d163bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8537a87f0d58bfca</t>
+          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Specialist, Software Engineering</t>
+          <t>ProBridge - Junior Snowflake Database Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BetaNXT</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,77 +2096,77 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b276cb63efa2d3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full- stack Engineer 4 - Capital One Shopping Tech (Categories Team) (Remote - Eligible)</t>
+          <t>ProBridge - Junior Snowflake Database Administrator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7893e5b1e4d9ff22</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab9ab4b8aed789a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Disputes Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chestertown, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
+          <t>https://www.indeed.com/viewjob?jk=54102d5fe6d163bd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8537a87f0d58bfca</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
+          <t>Senior Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aledade</t>
+          <t>BetaNXT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data and Platform Engineer</t>
+          <t>Integration Engineer 3 (Email/ProofPoint)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
+          <t>https://www.indeed.com/viewjob?jk=957ee504301bf4ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac96998021af3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c19b3b22378c8efc</t>
+          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Direct Client for Contact Center Architect Healthcare with AWS Connect</t>
+          <t>Full- stack Engineer 4 - Capital One Shopping Tech (Categories Team) (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3285dc43ed16da74</t>
+          <t>https://www.indeed.com/viewjob?jk=7893e5b1e4d9ff22</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAP S/4HANA Material Master Solution Architect / Senior MM Architect</t>
+          <t>Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>sdna global</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63f66f6aa5ca957</t>
+          <t>https://www.indeed.com/viewjob?jk=39e65aefb15b68ca</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02c5537c36a52ab</t>
+          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Disputes Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7519f106646cfafb</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Database Administrator - San Juan, PR</t>
+          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Aledade</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
+          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Technical Implementations Specialist (US)</t>
+          <t>Senior Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MEASURED</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aegis Mobile</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Power BI, Tableau, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cddb3162ff0a10d8</t>
+          <t>https://www.indeed.com/viewjob?jk=aac96998021af3ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d911c664f1ca9e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c19b3b22378c8efc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Direct Client for Contact Center Architect Healthcare with AWS Connect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
+          <t>https://www.indeed.com/viewjob?jk=3285dc43ed16da74</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Senior AI Engineer - US</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Typeform</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,46 +2722,46 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MLflow, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0022787a9f1c8382</t>
+          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dc299c4f5e424b</t>
+          <t>https://www.indeed.com/viewjob?jk=b02c5537c36a52ab</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator - San Juan, PR</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,15 +2823,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, Power BI, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cef3fbaab3f7c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Sr. Technical Implementations Specialist (US)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Superior Automotive Group</t>
+          <t>MEASURED</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, BigQuery, Dataflow, Vertex AI, Dimensional Modeling, dbt, Power BI, Tableau, Splunk, CI/CD</t>
+          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b32326f024eeaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>All IT Solutions LLC</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b9a73315ee85ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3d911c664f1ca9e3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Aegis Mobile</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Power BI, Tableau, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd065039757b55c7</t>
+          <t>https://www.indeed.com/viewjob?jk=cddb3162ff0a10d8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Developer in Test</t>
+          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56dd2ecf0c554e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd0eafd97ddc943</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Trimark Associates, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
+          <t>https://www.indeed.com/viewjob?jk=96810a7a6dbdd75a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Java Developer (SAP BTP/CAP)</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261609512021b9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae77aaad96ec33c1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Java Developer (SAP BTP/CAP)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d251cc0fd62f24</t>
+          <t>https://www.indeed.com/viewjob?jk=42eb97c80e2c8216</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,42 +3121,1372 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=078b97b2887a3962</t>
+          <t>https://www.indeed.com/viewjob?jk=accc0a915fc209c5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3b1fc7d47dc22fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92d161b705c196d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4 (Java, AWS)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0307bf553f12270f</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4043d02ce95e238a</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24beeb2eb3b965af</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1b76875b0de3a36</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbd502d8d46c80b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd7b2b83e756812</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da2125e052c84e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bf5c97e77c90b18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5275118ed12fd241</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b405211329b437c</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ae0177c68a80ad9</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Python, Typescript)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f31e7024946559a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c00cdc257f308304</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad8d78256053c3dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa38f701dd207fff</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7597fda19c9e29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18346eea91456b61</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Integration Engineer 4 (Email / Proofpoint)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9efe526fa2eec9b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Integration Engineer 4 (MAC)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4e76e5180e0ec43</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Integration Engineer 4 (SAM)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e81d19fb4dc37cf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer - GCP</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Wilton, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7d98e46591e0185</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Ness Digital Engineering</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RCH Solutions</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Container Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0022787a9f1c8382</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ness Digital Engineering</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19dc299c4f5e424b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, Power BI, Terraform</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8cef3fbaab3f7c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Superior Automotive Group</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>IAM, BigQuery, Dataflow, Vertex AI, Dimensional Modeling, dbt, Power BI, Tableau, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b32326f024eeaf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Integration Engineer 4</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92b048797715a4f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>All IT Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80b9a73315ee85ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Developer in Test</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d56dd2ecf0c554e</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Trimark Associates, Inc.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Folsom, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (SAP BTP/CAP)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=261609512021b9dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (SAP BTP/CAP)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88d251cc0fd62f24</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>Software Engineer III- Java/Python, SQL, Databricks</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>JPMorganChase</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D115" t="n">
         <v>10.4</v>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, Tableau</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d42fb889c5ed759</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=078b97b2887a3962</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-22.xlsx
+++ b/results/job_matches_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Engineering</t>
+          <t>Part Time Teller (20 Hours), Castro Branch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FourLeaf Federal Credit Union</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18438b84428c657e</t>
+          <t>https://www.indeed.com/viewjob?jk=62e481a61bf24644</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
+          <t>Azure Databricks &amp; Agentic AI Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Orgill, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Collierville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
+          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full stack Developer</t>
+          <t>Mid-Level Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phizenix</t>
+          <t>Antra, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb607626dcebb23</t>
+          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mid-Level Java Full Stack Developer</t>
+          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Orgill, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Collierville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f9f03cfec0fc88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7165608cf370f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DEPLOY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99a75f70479356</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Veradigm</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febe1e7e8d9c2705</t>
+          <t>https://www.indeed.com/viewjob?jk=0993a1ced84ff494</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deepwatch</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
+          <t>https://www.indeed.com/viewjob?jk=297ea1a332be0e9f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,217 +1606,217 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef57e790e48920b</t>
+          <t>https://www.indeed.com/viewjob?jk=81e443465ca87ae2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e39056943f43af2b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Engineer, Information Systems Specialist 7</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
+          <t>https://www.indeed.com/viewjob?jk=e363619a2524b8aa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer II</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69597557ab5f1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=901a1050af2afd7e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer II</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb60941e0eaba4f</t>
+          <t>https://www.indeed.com/viewjob?jk=52db018588005157</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, MongoDB, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a89b0de664aa93</t>
+          <t>https://www.indeed.com/viewjob?jk=27c43d5e88d9c28b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c02567e875c724</t>
+          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Veradigm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>West Lafayette, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a9d0a4fe41bcb8</t>
+          <t>https://www.indeed.com/viewjob?jk=febe1e7e8d9c2705</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Deepwatch</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9908194ee52c240</t>
+          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d06caa1f573b5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer, Information Systems Specialist 7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80229a4fad29b8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e702bf50ec0d208</t>
+          <t>https://www.indeed.com/viewjob?jk=a69597557ab5f1ab</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Senior Cloud Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Southwest, PA, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb60941e0eaba4f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Southwest, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
+          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ProBridge - Junior Snowflake Database Administrator</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b276cb63efa2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab9ab4b8aed789a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b276cb63efa2d3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>ProBridge - Junior Snowflake Database Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chestertown, MD, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54102d5fe6d163bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab9ab4b8aed789a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Chestertown, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8537a87f0d58bfca</t>
+          <t>https://www.indeed.com/viewjob?jk=54102d5fe6d163bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Specialist, Software Engineering</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BetaNXT</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,59 +2236,59 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
+          <t>https://www.indeed.com/viewjob?jk=8537a87f0d58bfca</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Integration Engineer 3 (Email/ProofPoint)</t>
+          <t>Senior Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BetaNXT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957ee504301bf4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
+          <t>Integration Engineer 3 (Email/ProofPoint)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
+          <t>https://www.indeed.com/viewjob?jk=957ee504301bf4ad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full- stack Engineer 4 - Capital One Shopping Tech (Categories Team) (Remote - Eligible)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7893e5b1e4d9ff22</t>
+          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data and Platform Engineer</t>
+          <t>Full- stack Engineer 4 - Capital One Shopping Tech (Categories Team) (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e65aefb15b68ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7893e5b1e4d9ff22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sentara</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
+          <t>https://www.indeed.com/viewjob?jk=39e65aefb15b68ca</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Disputes Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
+          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Disputes Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Aledade</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data and Platform Engineer</t>
+          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Aledade</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
+          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac96998021af3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c19b3b22378c8efc</t>
+          <t>https://www.indeed.com/viewjob?jk=aac96998021af3ad</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Direct Client for Contact Center Architect Healthcare with AWS Connect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3285dc43ed16da74</t>
+          <t>https://www.indeed.com/viewjob?jk=c19b3b22378c8efc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - US</t>
+          <t>Direct Client for Contact Center Architect Healthcare with AWS Connect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Typeform</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MLflow, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
+          <t>https://www.indeed.com/viewjob?jk=3285dc43ed16da74</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior AI Engineer - US</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Typeform</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MLflow, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
+          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02c5537c36a52ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Database Administrator - San Juan, PR</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b02c5537c36a52ab</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Technical Implementations Specialist (US)</t>
+          <t>Database Administrator - San Juan, PR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MEASURED</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Technical Implementations Specialist (US)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>MEASURED</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d911c664f1ca9e3</t>
+          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Aegis Mobile</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Power BI, Tableau, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cddb3162ff0a10d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd0eafd97ddc943</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
+          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd0eafd97ddc943</t>
+          <t>https://www.indeed.com/viewjob?jk=96810a7a6dbdd75a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96810a7a6dbdd75a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae77aaad96ec33c1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae77aaad96ec33c1</t>
+          <t>https://www.indeed.com/viewjob?jk=42eb97c80e2c8216</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42eb97c80e2c8216</t>
+          <t>https://www.indeed.com/viewjob?jk=accc0a915fc209c5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accc0a915fc209c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b3b1fc7d47dc22fc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3b1fc7d47dc22fc</t>
+          <t>https://www.indeed.com/viewjob?jk=92d161b705c196d3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
+          <t>Full Stack Engineer 4 (Java, AWS)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d161b705c196d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0307bf553f12270f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Java, AWS)</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0307bf553f12270f</t>
+          <t>https://www.indeed.com/viewjob?jk=4043d02ce95e238a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043d02ce95e238a</t>
+          <t>https://www.indeed.com/viewjob?jk=24beeb2eb3b965af</t>
         </is>
       </c>
     </row>
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24beeb2eb3b965af</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b76875b0de3a36</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b76875b0de3a36</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd502d8d46c80b1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd502d8d46c80b1</t>
+          <t>https://www.indeed.com/viewjob?jk=afd7b2b83e756812</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd7b2b83e756812</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2125e052c84e5</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2125e052c84e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf5c97e77c90b18</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf5c97e77c90b18</t>
+          <t>https://www.indeed.com/viewjob?jk=5275118ed12fd241</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5275118ed12fd241</t>
+          <t>https://www.indeed.com/viewjob?jk=9b405211329b437c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b405211329b437c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae0177c68a80ad9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full-stack Engineer 4 (Python, Typescript)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae0177c68a80ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f31e7024946559a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Typescript)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f31e7024946559a</t>
+          <t>https://www.indeed.com/viewjob?jk=c00cdc257f308304</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00cdc257f308304</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8d78256053c3dc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8d78256053c3dc</t>
+          <t>https://www.indeed.com/viewjob?jk=aa38f701dd207fff</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa38f701dd207fff</t>
+          <t>https://www.indeed.com/viewjob?jk=f7597fda19c9e29f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7597fda19c9e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=18346eea91456b61</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18346eea91456b61</t>
+          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
+          <t>Integration Engineer 4 (Email / Proofpoint)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
+          <t>https://www.indeed.com/viewjob?jk=9efe526fa2eec9b7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (Email / Proofpoint)</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9efe526fa2eec9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Integration Engineer 4 (MAC)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e76e5180e0ec43</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (MAC)</t>
+          <t>Integration Engineer 4 (SAM)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e76e5180e0ec43</t>
+          <t>https://www.indeed.com/viewjob?jk=e81d19fb4dc37cf8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (SAM)</t>
+          <t>Cloud Platform Engineer - GCP</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Wilton, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e81d19fb4dc37cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d98e46591e0185</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - GCP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wilton, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d98e46591e0185</t>
+          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,19 +4031,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
+          <t>https://www.indeed.com/viewjob?jk=0022787a9f1c8382</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0022787a9f1c8382</t>
+          <t>https://www.indeed.com/viewjob?jk=19dc299c4f5e424b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration Engineer 4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dc299c4f5e424b</t>
+          <t>https://www.indeed.com/viewjob?jk=92b048797715a4f2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>All IT Solutions LLC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, Power BI, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cef3fbaab3f7c3</t>
+          <t>https://www.indeed.com/viewjob?jk=80b9a73315ee85ae</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Superior Automotive Group</t>
+          <t>Trimark Associates, Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, BigQuery, Dataflow, Vertex AI, Dimensional Modeling, dbt, Power BI, Tableau, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b32326f024eeaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Integration Engineer 4</t>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4240,251 +4240,6 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92b048797715a4f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>All IT Solutions LLC</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80b9a73315ee85ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Software Developer in Test</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Splunk, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56dd2ecf0c554e</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Trimark Associates, Inc.</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Folsom, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Java Developer (SAP BTP/CAP)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=261609512021b9dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Java Developer (SAP BTP/CAP)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88d251cc0fd62f24</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Java/Python, SQL, Databricks</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, Tableau</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d42fb889c5ed759</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Alliance Health Plan</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=078b97b2887a3962</t>
         </is>

--- a/results/job_matches_2026-09-22.xlsx
+++ b/results/job_matches_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gentiva</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947423e1243398ca</t>
+          <t>https://www.indeed.com/viewjob?jk=10920ada24a70c04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer - Gen AI</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311b3d4d764c329</t>
+          <t>https://www.indeed.com/viewjob?jk=947423e1243398ca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS)</t>
+          <t>Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785ed8543590d56</t>
+          <t>https://www.indeed.com/viewjob?jk=9311b3d4d764c329</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Engineer 4 (Python, AWS)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30216af3fb095a16</t>
+          <t>https://www.indeed.com/viewjob?jk=6785ed8543590d56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pj Dick-Trumbull-Lindy Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=30216af3fb095a16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pj Dick-Trumbull-Lindy Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wexford, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,54 +671,54 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e707c3d7c8fd8897</t>
+          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Risk Tech)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc3d67e2533b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=195d724701bfe29e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Data Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, S3, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc3d67e2533b3c1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Larry H. Miller</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Step Functions, S3, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740a0acafa426fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Data and Integration</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Larry H. Miller</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, Azure, Databricks, GCP, BigQuery, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, SNS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cef3158b77fad33</t>
+          <t>https://www.indeed.com/viewjob?jk=6740a0acafa426fb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Software Engineer - Data and Integration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, SQS, SNS, Azure, Databricks, GCP, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cef3158b77fad33</t>
         </is>
       </c>
     </row>
@@ -888,52 +888,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Agentic AI Databricks</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad676d0583954a5</t>
+          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Databricks &amp; Agentic AI Architect</t>
+          <t>Engineer – Application</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Federated Hermes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Warrendale, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mid-Level Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad676d0583954a5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
+          <t>Azure Databricks &amp; Agentic AI Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Orgill, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Collierville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
+          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6329)</t>
+          <t>Mid-Level Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Antra, Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4007bc63b344853</t>
+          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ShipStation Global</t>
+          <t>Orgill, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Collierville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=028e43335938f143</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ShipStation Global</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5966248554dc0bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6425afe8b03c9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6425afe8b03c9</t>
+          <t>https://www.indeed.com/viewjob?jk=69bea3079274e464</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bea3079274e464</t>
+          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77aeab60d6ba5f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e448fd868464b75d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Expert</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Direct Travel</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e448fd868464b75d</t>
+          <t>https://www.indeed.com/viewjob?jk=f790e3f3013d99d9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Expert</t>
+          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f790e3f3013d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b781fa7970847c14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
+          <t>Summer 2027 Intern: Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,94 +1336,94 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781fa7970847c14</t>
+          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern: Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Live Oak Bank</t>
+          <t>US Tiger Securities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Hive, Spark, PySpark, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
+          <t>https://www.indeed.com/viewjob?jk=573ee0a7b1fef58d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Boats Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, ECS, IAM, RDS, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917ce891fbb59294</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7165608cf370f2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d93b899dbf5eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99a75f70479356</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7165608cf370f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0993a1ced84ff494</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99a75f70479356</t>
+          <t>https://www.indeed.com/viewjob?jk=297ea1a332be0e9f</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0993a1ced84ff494</t>
+          <t>https://www.indeed.com/viewjob?jk=81e443465ca87ae2</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ea1a332be0e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e39056943f43af2b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e443465ca87ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=e363619a2524b8aa</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39056943f43af2b</t>
+          <t>https://www.indeed.com/viewjob?jk=901a1050af2afd7e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e363619a2524b8aa</t>
+          <t>https://www.indeed.com/viewjob?jk=52db018588005157</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901a1050af2afd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=27c43d5e88d9c28b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52db018588005157</t>
+          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Data Engineer-5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c43d5e88d9c28b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb259aa46cf4c5ed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DEPLOY</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Database Engineer, Information Systems Specialist 7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Veradigm</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febe1e7e8d9c2705</t>
+          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Architect – AI &amp; Intelligent Applications</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deepwatch</t>
+          <t>Excelerate Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
+          <t>https://www.indeed.com/viewjob?jk=5f02d3f19c8a05a4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>Chestertown, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=54102d5fe6d163bd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Database Engineer, Information Systems Specialist 7</t>
+          <t>Senior Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>BetaNXT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer II</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southwest, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69597557ab5f1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer II</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb60941e0eaba4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Data Engineer - AWS, Snowflake</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Southwest, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e3740b07510bf369</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Integration Engineer 3 (Email/ProofPoint)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,137 +2106,137 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
+          <t>https://www.indeed.com/viewjob?jk=957ee504301bf4ad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ProBridge - Junior Snowflake Database Administrator</t>
+          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b276cb63efa2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ProBridge - Junior Snowflake Database Administrator</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Cloud Storage, Snowflake, Time Travel, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab9ab4b8aed789a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chestertown, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54102d5fe6d163bd</t>
+          <t>https://www.indeed.com/viewjob?jk=39e65aefb15b68ca</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8537a87f0d58bfca</t>
+          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Specialist, Software Engineering</t>
+          <t>Senior Disputes Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BetaNXT</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Integration Engineer 3 (Email/ProofPoint)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957ee504301bf4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
+          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Aledade</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
+          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full- stack Engineer 4 - Capital One Shopping Tech (Categories Team) (Remote - Eligible)</t>
+          <t>Database Administrator - San Juan, PR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7893e5b1e4d9ff22</t>
+          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data and Platform Engineer</t>
+          <t>Software Engineer 2 (Gen AI, LLM, Spring Boot)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e65aefb15b68ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab40f0fb4a43c1e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer 2 (Gen AI, LLM, Spring Boot)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sentara</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
+          <t>https://www.indeed.com/viewjob?jk=b327e81664e3144a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Disputes Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
+          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Sr. Technical Implementations Specialist (US)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MEASURED</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
+          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
+          <t>Senior AI Engineer - US</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aledade</t>
+          <t>Typeform</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MLflow, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data and Platform Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab165c224f9bf41</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac96998021af3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd0eafd97ddc943</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c19b3b22378c8efc</t>
+          <t>https://www.indeed.com/viewjob?jk=96810a7a6dbdd75a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Direct Client for Contact Center Architect Healthcare with AWS Connect</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3285dc43ed16da74</t>
+          <t>https://www.indeed.com/viewjob?jk=ae77aaad96ec33c1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - US</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Typeform</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MLflow, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
+          <t>https://www.indeed.com/viewjob?jk=42eb97c80e2c8216</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
+          <t>https://www.indeed.com/viewjob?jk=accc0a915fc209c5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02c5537c36a52ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b3b1fc7d47dc22fc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Database Administrator - San Juan, PR</t>
+          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
+          <t>https://www.indeed.com/viewjob?jk=92d161b705c196d3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Technical Implementations Specialist (US)</t>
+          <t>Full Stack Engineer 4 (Java, AWS)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MEASURED</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=0307bf553f12270f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd0eafd97ddc943</t>
+          <t>https://www.indeed.com/viewjob?jk=4043d02ce95e238a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96810a7a6dbdd75a</t>
+          <t>https://www.indeed.com/viewjob?jk=24beeb2eb3b965af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae77aaad96ec33c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b76875b0de3a36</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42eb97c80e2c8216</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd502d8d46c80b1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accc0a915fc209c5</t>
+          <t>https://www.indeed.com/viewjob?jk=afd7b2b83e756812</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3b1fc7d47dc22fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2125e052c84e5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d161b705c196d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf5c97e77c90b18</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Java, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0307bf553f12270f</t>
+          <t>https://www.indeed.com/viewjob?jk=5275118ed12fd241</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043d02ce95e238a</t>
+          <t>https://www.indeed.com/viewjob?jk=9b405211329b437c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24beeb2eb3b965af</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae0177c68a80ad9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Python, Typescript)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b76875b0de3a36</t>
+          <t>https://www.indeed.com/viewjob?jk=8f31e7024946559a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd502d8d46c80b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c00cdc257f308304</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd7b2b83e756812</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8d78256053c3dc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2125e052c84e5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa38f701dd207fff</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf5c97e77c90b18</t>
+          <t>https://www.indeed.com/viewjob?jk=f7597fda19c9e29f</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5275118ed12fd241</t>
+          <t>https://www.indeed.com/viewjob?jk=18346eea91456b61</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3492,28 +3492,28 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b405211329b437c</t>
+          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,50 +3523,50 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae0177c68a80ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Typescript)</t>
+          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f31e7024946559a</t>
+          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Integration Engineer 4 (Email / Proofpoint)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00cdc257f308304</t>
+          <t>https://www.indeed.com/viewjob?jk=9efe526fa2eec9b7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,11 +3628,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8d78256053c3dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Integration Engineer 4 (MAC)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,15 +3663,15 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa38f701dd207fff</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e76e5180e0ec43</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Integration Engineer 4 (SAM)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,15 +3698,15 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7597fda19c9e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=e81d19fb4dc37cf8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Cloud Platform Engineer - GCP</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilton, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18346eea91456b61</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d98e46591e0185</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
+          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (Email / Proofpoint)</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9efe526fa2eec9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Gen AI Engineer-5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,24 +3846,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fcc298a65fe517f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (MAC)</t>
+          <t>Integration Engineer 4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e76e5180e0ec43</t>
+          <t>https://www.indeed.com/viewjob?jk=92b048797715a4f2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (SAM)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>All IT Solutions LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e81d19fb4dc37cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=80b9a73315ee85ae</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - GCP</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Resideo</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wilton, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d98e46591e0185</t>
+          <t>https://www.indeed.com/viewjob?jk=6f3ccdfade853d8f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Full Stack (FES)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
+          <t>https://www.indeed.com/viewjob?jk=e95812a1a87ee87c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Senior Software Engineer, Full Stack (FES)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
+          <t>https://www.indeed.com/viewjob?jk=f0dd1357e631ea44</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Trimark Associates, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0022787a9f1c8382</t>
+          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>HPC Windows Server Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,157 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Photon, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dc299c4f5e424b</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Integration Engineer 4</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92b048797715a4f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>All IT Solutions LLC</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80b9a73315ee85ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Trimark Associates, Inc.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Folsom, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Alliance Health Plan</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=078b97b2887a3962</t>
+          <t>https://www.indeed.com/viewjob?jk=518ee0c62a254d22</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-22.xlsx
+++ b/results/job_matches_2026-09-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Database Engineer- Arlington, VA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gentiva</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,129 +486,129 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10920ada24a70c04</t>
+          <t>https://www.indeed.com/viewjob?jk=61eae97728d8e35d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gentiva</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947423e1243398ca</t>
+          <t>https://www.indeed.com/viewjob?jk=10920ada24a70c04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer - Gen AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Coca Cola Southwest Beverages</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9311b3d4d764c329</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f627225261b22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS)</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Oshkosh Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785ed8543590d56</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -631,29 +631,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30216af3fb095a16</t>
+          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Data Engineer 4 (Python, AWS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pj Dick-Trumbull-Lindy Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6785ed8543590d56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,139 +696,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195d724701bfe29e</t>
+          <t>https://www.indeed.com/viewjob?jk=30216af3fb095a16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Risk Tech)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc3d67e2533b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, S3, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
+          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Larry H. Miller</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740a0acafa426fb</t>
+          <t>https://www.indeed.com/viewjob?jk=195d724701bfe29e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Data and Integration</t>
+          <t>Data Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, Azure, Databricks, GCP, BigQuery, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,444 +846,444 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cef3158b77fad33</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc3d67e2533b3c1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Part Time Teller (20 Hours), Castro Branch</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Step Functions, S3, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e481a61bf24644</t>
+          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Agentic AI Databricks</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Larry H. Miller</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, SNS, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=6740a0acafa426fb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer – Application</t>
+          <t>Part Time Teller (20 Hours), Castro Branch</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Federated Hermes</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Warrendale, PA, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=62e481a61bf24644</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Agentic AI Databricks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad676d0583954a5</t>
+          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Databricks &amp; Agentic AI Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Seek Now</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
+          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mid-Level Java Full Stack Developer</t>
+          <t>Senior Full-stack .NET/C# Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Liaison International</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, ECS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f598645d678c04ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4da03412f0454158</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Dir Digital Ecommerce and Marketing Engineering</t>
+          <t>Senior Data/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Orgill, Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Collierville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d080c1f88083cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5fae1eed697d12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Engineer – Application</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Federated Hermes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Warrendale, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6425afe8b03c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SOW198 Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AnewHealth</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bea3079274e464</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbc4fb78c7362b3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad676d0583954a5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Composable Commerce Solution Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Direct Travel</t>
+          <t>Litmus7 System Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, Azure, GCP, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e448fd868464b75d</t>
+          <t>https://www.indeed.com/viewjob?jk=2596f5d3398a102f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer, Expert</t>
+          <t>Azure Databricks &amp; Agentic AI Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f790e3f3013d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781fa7970847c14</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6425afe8b03c9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern: Data Engineering</t>
+          <t>Sr. ML Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Live Oak Bank</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
+          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
         </is>
       </c>
     </row>
@@ -1348,55 +1348,55 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>US Tiger Securities</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Hive, Spark, PySpark, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573ee0a7b1fef58d</t>
+          <t>https://www.indeed.com/viewjob?jk=e448fd868464b75d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>WorkOS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7165608cf370f2</t>
+          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Summer 2027 Intern: Data Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99a75f70479356</t>
+          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>US Tiger Securities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Hive, Spark, PySpark, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0993a1ced84ff494</t>
+          <t>https://www.indeed.com/viewjob?jk=573ee0a7b1fef58d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ea1a332be0e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7165608cf370f2</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e443465ca87ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99a75f70479356</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39056943f43af2b</t>
+          <t>https://www.indeed.com/viewjob?jk=0993a1ced84ff494</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e363619a2524b8aa</t>
+          <t>https://www.indeed.com/viewjob?jk=297ea1a332be0e9f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901a1050af2afd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=81e443465ca87ae2</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52db018588005157</t>
+          <t>https://www.indeed.com/viewjob?jk=e39056943f43af2b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c43d5e88d9c28b</t>
+          <t>https://www.indeed.com/viewjob?jk=e363619a2524b8aa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DEPLOY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
+          <t>https://www.indeed.com/viewjob?jk=901a1050af2afd7e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer-5</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,129 +1791,129 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb259aa46cf4c5ed</t>
+          <t>https://www.indeed.com/viewjob?jk=52db018588005157</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=27c43d5e88d9c28b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Database Engineer, Information Systems Specialist 7</t>
+          <t>Forward Deployed Engineer, Client Solutions Group</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
+          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Architect – AI &amp; Intelligent Applications</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Excelerate Technologies</t>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f02d3f19c8a05a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chestertown, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54102d5fe6d163bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Specialist, Software Engineering</t>
+          <t>Data Engineer-5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BetaNXT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb259aa46cf4c5ed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Southwest, PA, US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Database Engineer, Information Systems Specialist 7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c78d540024d7df8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, Snowflake</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,137 +2071,137 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3740b07510bf369</t>
+          <t>https://www.indeed.com/viewjob?jk=159ff5be89845750</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Integration Engineer 3 (Email/ProofPoint)</t>
+          <t>Sr Java MS Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957ee504301bf4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e4991e3d38b8257d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
+          <t>Full Stack Architect – AI &amp; Intelligent Applications</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Excelerate Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
+          <t>https://www.indeed.com/viewjob?jk=5f02d3f19c8a05a4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Architect, Corporate Services</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, Microsoft SSIS, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data and Platform Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e65aefb15b68ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sentara</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
+          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Disputes Data Engineer</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southwest, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
+          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Sr. Solutions Engineer - Games</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
+          <t>Full-Stack Engineer 5 (Java, AWS, Kafka)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aledade</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=df64f895efc7335d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data and Platform Engineer</t>
+          <t>Data Engineer - AWS, Snowflake</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka, ETL</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
+          <t>https://www.indeed.com/viewjob?jk=e3740b07510bf369</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Administrator - San Juan, PR</t>
+          <t>Integration Engineer 3 (Email/ProofPoint)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab623860746e35b7</t>
+          <t>https://www.indeed.com/viewjob?jk=957ee504301bf4ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Gen AI, LLM, Spring Boot)</t>
+          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab40f0fb4a43c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Gen AI, LLM, Spring Boot)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b327e81664e3144a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
+          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Technical Implementations Specialist (US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MEASURED</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=05afa083475c5a6e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - US</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Typeform</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MLflow, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
+          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Disputes Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab165c224f9bf41</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd0eafd97ddc943</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
+          <t>Senior Software Engineer I - Data &amp; Algorithm Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Aledade</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96810a7a6dbdd75a</t>
+          <t>https://www.indeed.com/viewjob?jk=89c27477c100ca2e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae77aaad96ec33c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Idaho Falls, ID, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42eb97c80e2c8216</t>
+          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS)</t>
+          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accc0a915fc209c5</t>
+          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior AI Engineer - US</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Typeform</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MLflow, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3b1fc7d47dc22fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Typescript, Vue, AWS)</t>
+          <t>C# Full Stack Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d161b705c196d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Java, AWS)</t>
+          <t>Software Engineer 2 (Gen AI, LLM, Spring Boot)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0307bf553f12270f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab40f0fb4a43c1e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+          <t>Software Engineer 2 (Gen AI, LLM, Spring Boot)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043d02ce95e238a</t>
+          <t>https://www.indeed.com/viewjob?jk=b327e81664e3144a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24beeb2eb3b965af</t>
+          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3011,19 +3011,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b76875b0de3a36</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e4280958473ee4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3046,19 +3046,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd502d8d46c80b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab165c224f9bf41</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,32 +3068,32 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd7b2b83e756812</t>
+          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,50 +3103,50 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2125e052c84e5</t>
+          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf5c97e77c90b18</t>
+          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Integration Engineer 4 (Email / Proofpoint)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,15 +3173,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5275118ed12fd241</t>
+          <t>https://www.indeed.com/viewjob?jk=9efe526fa2eec9b7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b405211329b437c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Integration Engineer 4 (MAC)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,15 +3243,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae0177c68a80ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e76e5180e0ec43</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Typescript)</t>
+          <t>Integration Engineer 4 (SAM)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,15 +3278,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f31e7024946559a</t>
+          <t>https://www.indeed.com/viewjob?jk=e81d19fb4dc37cf8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Cloud Platform Engineer - GCP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilton, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00cdc257f308304</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d98e46591e0185</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8d78256053c3dc</t>
+          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,94 +3401,94 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa38f701dd207fff</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7597fda19c9e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18346eea91456b61</t>
+          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Gen AI Engineer-5</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
+          <t>https://www.indeed.com/viewjob?jk=4fcc298a65fe517f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Engineer, Performance Management</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0346f80c455f7d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Trimark Associates, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
+          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (Email / Proofpoint)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Resideo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9efe526fa2eec9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f3ccdfade853d8f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Senior Software Engineer, Full Stack (FES)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e95812a1a87ee87c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (MAC)</t>
+          <t>Senior Software Engineer, Full Stack (FES)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e76e5180e0ec43</t>
+          <t>https://www.indeed.com/viewjob?jk=f0dd1357e631ea44</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (SAM)</t>
+          <t>HPC Windows Server Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,400 +3706,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Photon, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e81d19fb4dc37cf8</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer - GCP</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>ASML</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Wilton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d98e46591e0185</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Ness Digital Engineering</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>GCP Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>RCH Solutions</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Airflow</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1578e51c74106b</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Gen AI Engineer-5</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fcc298a65fe517f</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Integration Engineer 4</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92b048797715a4f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>All IT Solutions LLC</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80b9a73315ee85ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Resideo</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3ccdfade853d8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack (FES)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Fanatics</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e95812a1a87ee87c</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack (FES)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Fanatics</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dd1357e631ea44</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Trimark Associates, Inc.</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Folsom, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>HPC Windows Server Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Photon, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=518ee0c62a254d22</t>
         </is>
